--- a/data/trans_camb/IP19C03-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/IP19C03-Habitat-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-16,12; 5,08</t>
+          <t>-15,98; 5,19</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-10,13; 12,79</t>
+          <t>-10,83; 11,12</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-12,04; 7,85</t>
+          <t>-13,38; 8,01</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-5,22; 16,7</t>
+          <t>-4,48; 16,64</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-12,65; 8,51</t>
+          <t>-11,7; 7,08</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-15,13; 4,73</t>
+          <t>-15,05; 4,37</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-7,2; 7,37</t>
+          <t>-7,0; 7,65</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-8,97; 6,03</t>
+          <t>-8,28; 6,71</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-11,37; 3,59</t>
+          <t>-11,4; 3,94</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-61,18; 36,03</t>
+          <t>-61,59; 34,23</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-40,0; 84,65</t>
+          <t>-42,34; 77,82</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-48,09; 52,68</t>
+          <t>-48,02; 54,65</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-22,55; 126,8</t>
+          <t>-22,88; 118,58</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-55,16; 66,76</t>
+          <t>-54,69; 54,79</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-68,87; 44,07</t>
+          <t>-66,85; 40,82</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-32,29; 47,88</t>
+          <t>-31,41; 47,1</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-39,52; 39,38</t>
+          <t>-36,65; 43,29</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-52,08; 22,75</t>
+          <t>-49,31; 23,65</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-7,28; 11,67</t>
+          <t>-7,43; 11,23</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-14,47; 3,31</t>
+          <t>-14,51; 4,09</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-21,66; -4,2</t>
+          <t>-22,03; -4,36</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-3,7; 14,12</t>
+          <t>-3,71; 12,5</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-3,58; 13,56</t>
+          <t>-5,03; 13,47</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-8,11; 7,75</t>
+          <t>-8,31; 7,6</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-3,14; 10,01</t>
+          <t>-2,87; 9,36</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-6,42; 5,78</t>
+          <t>-6,85; 5,87</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-11,93; -0,13</t>
+          <t>-12,16; -0,34</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-23,32; 53,15</t>
+          <t>-24,85; 54,1</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-46,62; 14,59</t>
+          <t>-46,33; 19,22</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-70,61; -18,85</t>
+          <t>-70,24; -17,45</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-16,28; 94,79</t>
+          <t>-16,98; 87,17</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-17,44; 93,36</t>
+          <t>-20,93; 96,19</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-35,92; 56,91</t>
+          <t>-36,39; 54,34</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-12,83; 51,65</t>
+          <t>-11,43; 47,84</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-26,12; 30,62</t>
+          <t>-26,95; 30,45</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-48,74; -0,02</t>
+          <t>-46,6; -1,3</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-15,1; 5,26</t>
+          <t>-15,32; 5,24</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-15,92; 5,1</t>
+          <t>-16,16; 4,5</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-6,11; 15,8</t>
+          <t>-6,02; 17,37</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-4,32; 15,43</t>
+          <t>-4,8; 14,52</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-2,65; 16,99</t>
+          <t>-4,66; 17,57</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-8,16; 10,52</t>
+          <t>-7,74; 11,47</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-6,84; 7,84</t>
+          <t>-6,96; 7,8</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-6,1; 8,51</t>
+          <t>-5,88; 8,62</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-4,74; 10,46</t>
+          <t>-4,57; 10,58</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-54,54; 32,06</t>
+          <t>-54,38; 33,38</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-58,42; 34,51</t>
+          <t>-59,63; 31,83</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-25,89; 96,54</t>
+          <t>-25,57; 108,51</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-21,9; 134,09</t>
+          <t>-23,31; 131,76</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-15,31; 143,56</t>
+          <t>-21,88; 148,74</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-40,59; 85,44</t>
+          <t>-37,31; 112,12</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-30,0; 52,43</t>
+          <t>-30,59; 52,7</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-29,24; 55,22</t>
+          <t>-26,73; 59,98</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-20,95; 70,08</t>
+          <t>-21,8; 67,97</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-4,07; 14,35</t>
+          <t>-4,11; 14,37</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-11,3; 4,18</t>
+          <t>-10,36; 5,53</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-8,22; 8,14</t>
+          <t>-8,89; 7,91</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-15,91; -0,14</t>
+          <t>-15,93; 0,75</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-13,5; 2,25</t>
+          <t>-13,82; 2,31</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-11,71; 6,29</t>
+          <t>-10,53; 6,94</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-7,63; 5,02</t>
+          <t>-8,0; 4,75</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-10,59; 1,7</t>
+          <t>-10,27; 1,64</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-7,8; 4,85</t>
+          <t>-7,75; 4,78</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-24,07; 149,02</t>
+          <t>-23,95; 147,24</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-60,65; 38,73</t>
+          <t>-58,02; 61,97</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-46,94; 87,38</t>
+          <t>-48,81; 85,06</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-74,25; 2,22</t>
+          <t>-73,47; 15,64</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-63,84; 19,56</t>
+          <t>-63,8; 23,28</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-55,87; 53,89</t>
+          <t>-51,69; 56,86</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-42,35; 42,4</t>
+          <t>-42,94; 39,03</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-54,56; 13,93</t>
+          <t>-54,35; 15,97</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-41,22; 39,72</t>
+          <t>-42,92; 38,99</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-5,0; 5,29</t>
+          <t>-5,18; 4,42</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-8,38; 1,02</t>
+          <t>-8,46; 0,81</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-7,88; 1,33</t>
+          <t>-7,82; 1,89</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-3,23; 6,51</t>
+          <t>-2,76; 6,56</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-3,74; 4,66</t>
+          <t>-4,12; 5,02</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-5,72; 3,86</t>
+          <t>-5,36; 3,73</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-2,32; 4,12</t>
+          <t>-2,45; 4,37</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-4,76; 1,81</t>
+          <t>-4,86; 2,08</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-5,58; 0,9</t>
+          <t>-5,62; 1,28</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-22,88; 29,39</t>
+          <t>-22,41; 23,74</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-35,96; 6,31</t>
+          <t>-36,81; 3,98</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-33,46; 6,82</t>
+          <t>-34,09; 10,73</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-16,11; 43,07</t>
+          <t>-14,58; 42,17</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-18,81; 29,7</t>
+          <t>-21,09; 32,55</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-28,74; 25,27</t>
+          <t>-27,76; 24,09</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-11,1; 24,06</t>
+          <t>-12,37; 25,28</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-22,96; 10,4</t>
+          <t>-23,22; 12,21</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-27,14; 5,49</t>
+          <t>-27,12; 7,02</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP19C03-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/IP19C03-Habitat-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-15,98; 5,19</t>
+          <t>-14,71; 5,14</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-10,83; 11,12</t>
+          <t>-10,09; 12,61</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-13,38; 8,01</t>
+          <t>-12,48; 9,31</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-4,48; 16,64</t>
+          <t>-4,98; 16,16</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-11,7; 7,08</t>
+          <t>-12,28; 6,73</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-15,05; 4,37</t>
+          <t>-15,58; 5,21</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-7,0; 7,65</t>
+          <t>-7,47; 7,32</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-8,28; 6,71</t>
+          <t>-8,8; 6,14</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-11,4; 3,94</t>
+          <t>-11,13; 3,73</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-61,59; 34,23</t>
+          <t>-57,87; 35,73</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-42,34; 77,82</t>
+          <t>-40,61; 88,38</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-48,02; 54,65</t>
+          <t>-49,66; 63,71</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-22,88; 118,58</t>
+          <t>-23,09; 124,47</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-54,69; 54,79</t>
+          <t>-54,64; 53,38</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-66,85; 40,82</t>
+          <t>-67,39; 38,24</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-31,41; 47,1</t>
+          <t>-33,68; 45,41</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-36,65; 43,29</t>
+          <t>-36,73; 37,01</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-49,31; 23,65</t>
+          <t>-50,55; 22,06</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-7,43; 11,23</t>
+          <t>-7,51; 10,24</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-14,51; 4,09</t>
+          <t>-14,45; 3,52</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-22,03; -4,36</t>
+          <t>-21,51; -4,81</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-3,71; 12,5</t>
+          <t>-4,03; 13,52</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-5,03; 13,47</t>
+          <t>-4,73; 13,27</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-8,31; 7,6</t>
+          <t>-8,02; 7,35</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-2,87; 9,36</t>
+          <t>-2,38; 9,92</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-6,85; 5,87</t>
+          <t>-6,68; 5,93</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-12,16; -0,34</t>
+          <t>-12,12; -0,74</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-24,85; 54,1</t>
+          <t>-24,17; 47,46</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-46,33; 19,22</t>
+          <t>-46,88; 18,63</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-70,24; -17,45</t>
+          <t>-70,31; -21,12</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-16,98; 87,17</t>
+          <t>-16,96; 94,67</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-20,93; 96,19</t>
+          <t>-22,02; 89,82</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-36,39; 54,34</t>
+          <t>-35,3; 48,83</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-11,43; 47,84</t>
+          <t>-9,66; 51,9</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-26,95; 30,45</t>
+          <t>-26,68; 30,09</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-46,6; -1,3</t>
+          <t>-47,6; -3,19</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-15,32; 5,24</t>
+          <t>-14,25; 5,9</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-16,16; 4,5</t>
+          <t>-15,52; 4,22</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-6,02; 17,37</t>
+          <t>-7,23; 15,27</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-4,8; 14,52</t>
+          <t>-4,89; 15,1</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-4,66; 17,57</t>
+          <t>-2,87; 17,88</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-7,74; 11,47</t>
+          <t>-7,81; 11,28</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-6,96; 7,8</t>
+          <t>-6,69; 7,85</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-5,88; 8,62</t>
+          <t>-6,56; 8,68</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-4,57; 10,58</t>
+          <t>-4,46; 10,54</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-54,38; 33,38</t>
+          <t>-53,4; 37,4</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-59,63; 31,83</t>
+          <t>-56,41; 27,52</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-25,57; 108,51</t>
+          <t>-27,03; 93,99</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-23,31; 131,76</t>
+          <t>-25,4; 134,48</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-21,88; 148,74</t>
+          <t>-15,4; 153,89</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-37,31; 112,12</t>
+          <t>-37,7; 106,06</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-30,59; 52,7</t>
+          <t>-31,05; 53,88</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-26,73; 59,98</t>
+          <t>-30,83; 54,19</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-21,8; 67,97</t>
+          <t>-21,12; 71,8</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-4,11; 14,37</t>
+          <t>-3,98; 14,18</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-10,36; 5,53</t>
+          <t>-10,59; 5,14</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-8,89; 7,91</t>
+          <t>-9,8; 8,02</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-15,93; 0,75</t>
+          <t>-16,83; -0,36</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-13,82; 2,31</t>
+          <t>-14,13; 2,37</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-10,53; 6,94</t>
+          <t>-11,46; 6,43</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-8,0; 4,75</t>
+          <t>-7,58; 4,99</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-10,27; 1,64</t>
+          <t>-9,75; 1,49</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-7,75; 4,78</t>
+          <t>-7,4; 5,14</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-23,95; 147,24</t>
+          <t>-23,33; 154,89</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-58,02; 61,97</t>
+          <t>-58,84; 63,24</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-48,81; 85,06</t>
+          <t>-54,02; 83,76</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-73,47; 15,64</t>
+          <t>-73,61; 2,76</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-63,8; 23,28</t>
+          <t>-64,96; 19,97</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-51,69; 56,86</t>
+          <t>-56,5; 52,07</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-42,94; 39,03</t>
+          <t>-41,38; 43,27</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-54,35; 15,97</t>
+          <t>-53,22; 13,54</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-42,92; 38,99</t>
+          <t>-40,61; 42,57</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-5,18; 4,42</t>
+          <t>-5,39; 4,39</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-8,46; 0,81</t>
+          <t>-8,42; 0,92</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-7,82; 1,89</t>
+          <t>-8,06; 1,81</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-2,76; 6,56</t>
+          <t>-2,7; 7,02</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-4,12; 5,02</t>
+          <t>-3,96; 5,37</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-5,36; 3,73</t>
+          <t>-6,16; 3,24</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-2,45; 4,37</t>
+          <t>-2,59; 3,94</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-4,86; 2,08</t>
+          <t>-4,9; 1,66</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-5,62; 1,28</t>
+          <t>-5,36; 1,14</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-22,41; 23,74</t>
+          <t>-23,18; 23,69</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-36,81; 3,98</t>
+          <t>-36,93; 4,65</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-34,09; 10,73</t>
+          <t>-35,53; 9,96</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-14,58; 42,17</t>
+          <t>-13,5; 46,38</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-21,09; 32,55</t>
+          <t>-19,48; 35,17</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-27,76; 24,09</t>
+          <t>-30,57; 21,27</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-12,37; 25,28</t>
+          <t>-12,0; 22,23</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-23,22; 12,21</t>
+          <t>-23,47; 9,37</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-27,12; 7,02</t>
+          <t>-25,74; 6,74</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP19C03-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/IP19C03-Habitat-trans_camb.xlsx
@@ -529,14 +529,14 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -624,32 +624,32 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>5,94</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>-2,77</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>-5,56</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>-5,22</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>1,27</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>-1,92</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>5,94</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>-2,77</t>
-        </is>
-      </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>-5,53</t>
+          <t>-2,38</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>-3,98</t>
+          <t>-4,05</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-14,71; 5,14</t>
+          <t>-5,22; 16,7</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-10,09; 12,61</t>
+          <t>-12,65; 8,51</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-12,48; 9,31</t>
+          <t>-15,04; 4,73</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-4,98; 16,16</t>
+          <t>-16,12; 5,08</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-12,28; 6,73</t>
+          <t>-10,13; 12,79</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-15,58; 5,21</t>
+          <t>-12,52; 7,67</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-7,47; 7,32</t>
+          <t>-7,2; 7,37</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-8,8; 6,14</t>
+          <t>-8,97; 6,03</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-11,13; 3,73</t>
+          <t>-11,08; 3,49</t>
         </is>
       </c>
     </row>
@@ -730,32 +730,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>32,78%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>-15,29%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>-30,68%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
           <t>-25,34%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>6,19%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>-9,31%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>32,78%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>-15,29%</t>
-        </is>
-      </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>-30,53%</t>
+          <t>-11,57%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>-20,61%</t>
+          <t>-20,98%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-57,87; 35,73</t>
+          <t>-22,55; 126,8</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-40,61; 88,38</t>
+          <t>-55,16; 66,76</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-49,66; 63,71</t>
+          <t>-67,98; 43,4</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-23,09; 124,47</t>
+          <t>-61,18; 36,03</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-54,64; 53,38</t>
+          <t>-40,0; 84,65</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-67,39; 38,24</t>
+          <t>-49,75; 49,62</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-33,68; 45,41</t>
+          <t>-32,29; 47,88</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-36,73; 37,01</t>
+          <t>-39,52; 39,38</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-50,55; 22,06</t>
+          <t>-51,33; 22,02</t>
         </is>
       </c>
     </row>
@@ -840,32 +840,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>4,85</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>4,45</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>-1,05</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>1,65</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>-5,68</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>-13,24</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>4,85</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>4,45</t>
-        </is>
-      </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>-0,32</t>
+          <t>-13,48</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>-6,25</t>
+          <t>-6,85</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-7,51; 10,24</t>
+          <t>-3,7; 14,12</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-14,45; 3,52</t>
+          <t>-3,58; 13,56</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-21,51; -4,81</t>
+          <t>-8,78; 7,19</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-4,03; 13,52</t>
+          <t>-7,28; 11,67</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-4,73; 13,27</t>
+          <t>-14,47; 3,31</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-8,02; 7,35</t>
+          <t>-21,88; -4,37</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-2,38; 9,92</t>
+          <t>-3,14; 10,01</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-6,68; 5,93</t>
+          <t>-6,42; 5,78</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-12,12; -0,74</t>
+          <t>-12,28; -0,85</t>
         </is>
       </c>
     </row>
@@ -946,32 +946,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>26,04%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>23,93%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>-5,67%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>6,28%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>-21,66%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>-50,48%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>26,04%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>23,93%</t>
-        </is>
-      </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>-1,72%</t>
+          <t>-51,39%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>-27,9%</t>
+          <t>-30,59%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-24,17; 47,46</t>
+          <t>-16,28; 94,79</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-46,88; 18,63</t>
+          <t>-17,44; 93,36</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-70,31; -21,12</t>
+          <t>-38,86; 51,43</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-16,96; 94,67</t>
+          <t>-23,32; 53,15</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-22,02; 89,82</t>
+          <t>-46,62; 14,59</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-35,3; 48,83</t>
+          <t>-71,12; -19,4</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-9,66; 51,9</t>
+          <t>-12,83; 51,65</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-26,68; 30,09</t>
+          <t>-26,12; 30,62</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-47,6; -3,19</t>
+          <t>-50,64; -3,81</t>
         </is>
       </c>
     </row>
@@ -1056,32 +1056,32 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>5,14</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>7,46</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>1,74</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
           <t>-4,26</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>-5,85</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>4,09</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>5,14</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>7,46</t>
-        </is>
-      </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>1,47</t>
+          <t>2,78</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>2,7</t>
+          <t>2,28</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-14,25; 5,9</t>
+          <t>-4,32; 15,43</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-15,52; 4,22</t>
+          <t>-2,65; 16,99</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-7,23; 15,27</t>
+          <t>-7,79; 11,23</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-4,89; 15,1</t>
+          <t>-15,1; 5,26</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-2,87; 17,88</t>
+          <t>-15,92; 5,1</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-7,81; 11,28</t>
+          <t>-7,67; 13,35</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-6,69; 7,85</t>
+          <t>-6,84; 7,84</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-6,56; 8,68</t>
+          <t>-6,1; 8,51</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-4,46; 10,54</t>
+          <t>-4,83; 9,36</t>
         </is>
       </c>
     </row>
@@ -1162,32 +1162,32 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>31,78%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>46,08%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>10,73%</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
           <t>-19,5%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>-26,75%</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>18,7%</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>31,78%</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>46,08%</t>
-        </is>
-      </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>9,06%</t>
+          <t>12,73%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>14,33%</t>
+          <t>12,07%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-53,4; 37,4</t>
+          <t>-21,9; 134,09</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-56,41; 27,52</t>
+          <t>-15,31; 143,56</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-27,03; 93,99</t>
+          <t>-37,51; 93,23</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-25,4; 134,48</t>
+          <t>-54,54; 32,06</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-15,4; 153,89</t>
+          <t>-58,42; 34,51</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-37,7; 106,06</t>
+          <t>-29,18; 81,4</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-31,05; 53,88</t>
+          <t>-30,0; 52,43</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-30,83; 54,19</t>
+          <t>-29,24; 55,22</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-21,12; 71,8</t>
+          <t>-22,92; 62,67</t>
         </is>
       </c>
     </row>
@@ -1272,32 +1272,32 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>-7,57</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>-5,52</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>-3,52</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
           <t>4,8</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>-2,74</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>-0,57</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>-7,57</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>-5,52</t>
-        </is>
-      </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>-2,34</t>
+          <t>-0,48</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>-1,37</t>
+          <t>-1,95</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-3,98; 14,18</t>
+          <t>-15,91; -0,14</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-10,59; 5,14</t>
+          <t>-13,5; 2,25</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-9,8; 8,02</t>
+          <t>-12,62; 4,73</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-16,83; -0,36</t>
+          <t>-4,07; 14,35</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-14,13; 2,37</t>
+          <t>-11,3; 4,18</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-11,46; 6,43</t>
+          <t>-8,04; 8,52</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-7,58; 4,99</t>
+          <t>-7,63; 5,02</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-9,75; 1,49</t>
+          <t>-10,59; 1,7</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-7,4; 5,14</t>
+          <t>-8,29; 4,14</t>
         </is>
       </c>
     </row>
@@ -1378,32 +1378,32 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>-44,83%</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>-32,72%</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>-20,86%</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
           <t>34,86%</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr">
         <is>
           <t>-19,93%</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>-4,11%</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>-44,83%</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>-32,72%</t>
-        </is>
-      </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>-13,86%</t>
+          <t>-3,47%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>-8,97%</t>
+          <t>-12,76%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-23,33; 154,89</t>
+          <t>-74,25; 2,22</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-58,84; 63,24</t>
+          <t>-63,84; 19,56</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-54,02; 83,76</t>
+          <t>-59,13; 42,84</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-73,61; 2,76</t>
+          <t>-24,07; 149,02</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-64,96; 19,97</t>
+          <t>-60,65; 38,73</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-56,5; 52,07</t>
+          <t>-46,73; 94,24</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-41,38; 43,27</t>
+          <t>-42,35; 42,4</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-53,22; 13,54</t>
+          <t>-54,56; 13,93</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-40,61; 42,57</t>
+          <t>-43,9; 33,69</t>
         </is>
       </c>
     </row>
@@ -1488,32 +1488,32 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>1,85</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>0,65</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>-1,74</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
           <t>-0,1</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="G20" s="2" t="inlineStr">
         <is>
           <t>-3,75</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>-3,15</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>1,85</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>0,65</t>
-        </is>
-      </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>-1,28</t>
+          <t>-3,76</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>-2,26</t>
+          <t>-2,77</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-5,39; 4,39</t>
+          <t>-3,23; 6,51</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-8,42; 0,92</t>
+          <t>-3,74; 4,66</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-8,06; 1,81</t>
+          <t>-6,02; 3,32</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-2,7; 7,02</t>
+          <t>-5,0; 5,29</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-3,96; 5,37</t>
+          <t>-8,38; 1,02</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-6,16; 3,24</t>
+          <t>-8,51; 0,66</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-2,59; 3,94</t>
+          <t>-2,32; 4,12</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-4,9; 1,66</t>
+          <t>-4,76; 1,81</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-5,36; 1,14</t>
+          <t>-6,04; 0,48</t>
         </is>
       </c>
     </row>
@@ -1594,32 +1594,32 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>10,57%</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>3,69%</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>-9,93%</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
           <t>-0,47%</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="G22" s="2" t="inlineStr">
         <is>
           <t>-18,06%</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>-15,17%</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>10,57%</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>3,69%</t>
-        </is>
-      </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>-7,31%</t>
+          <t>-18,11%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>-11,83%</t>
+          <t>-14,49%</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-23,18; 23,69</t>
+          <t>-16,11; 43,07</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-36,93; 4,65</t>
+          <t>-18,81; 29,7</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-35,53; 9,96</t>
+          <t>-30,54; 22,43</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-13,5; 46,38</t>
+          <t>-22,88; 29,39</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-19,48; 35,17</t>
+          <t>-35,96; 6,31</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-30,57; 21,27</t>
+          <t>-36,3; 3,55</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-12,0; 22,23</t>
+          <t>-11,1; 24,06</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-23,47; 9,37</t>
+          <t>-22,96; 10,4</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-25,74; 6,74</t>
+          <t>-29,06; 3,04</t>
         </is>
       </c>
     </row>
